--- a/output/full_scan/batch_seq6_2026-08-20.xlsx
+++ b/output/full_scan/batch_seq6_2026-08-20.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O116"/>
+  <dimension ref="A1:O118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6472</v>
+        <v>6213</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1012.53338138134</v>
+        <v>1068.607289683494</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>445.5</v>
+        <v>510</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,49 +552,49 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>61.83481490818576</v>
+        <v>76.27121927597325</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>23.620047613312</v>
+        <v>24.35570982715817</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>3.628214293335278</v>
+        <v>0.2205791481160161</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>1.983735399739833</v>
+        <v>13.58025332568861</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6426</v>
+        <v>6472</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>852.0149151582463</v>
+        <v>1012.53338138134</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>250</v>
+        <v>445.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,13 +605,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>68.69198943485431</v>
+        <v>61.83481490818576</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>28.41087065880225</v>
+        <v>23.620047613312</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.412195713575163</v>
+        <v>3.628214293335278</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>7.330643692858704</v>
+        <v>1.983735399739833</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6265</v>
+        <v>6426</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>688.4993932816008</v>
+        <v>852.0149151582463</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>56.5</v>
+        <v>250</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>54.9528639039884</v>
+        <v>68.69198943485431</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>23.05954042428585</v>
+        <v>28.41087065880225</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.845091288354021</v>
+        <v>2.412195713575163</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.7957968288211996</v>
+        <v>7.330643692858704</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6173</v>
+        <v>6225</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>682.9449437044678</v>
+        <v>786.0734029742067</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>221</v>
+        <v>58.9</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,13 +711,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>56.29945520593792</v>
+        <v>92.0226209332362</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>23.14692840506363</v>
+        <v>37.75500191100234</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3.59449437044678</v>
+        <v>1.707340297420674</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>8.345864534932186</v>
+        <v>3.280560123899323</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6214</v>
+        <v>6265</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>668.6864300536193</v>
+        <v>688.4993932816008</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>180</v>
+        <v>56.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>76.5122677229144</v>
+        <v>54.9528639039884</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>24.581916718812</v>
+        <v>23.05954042428585</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.9686430053619376</v>
+        <v>1.845091288354021</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>3.355433643820879</v>
+        <v>0.7957968288211996</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6187</v>
+        <v>6173</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>658.3232231159247</v>
+        <v>682.9449437044678</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1265</v>
+        <v>221</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>57.69850315503145</v>
+        <v>56.29945520593792</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>20.94702745828262</v>
+        <v>23.14692840506363</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.8620860935134772</v>
+        <v>3.59449437044678</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>24.7018904088973</v>
+        <v>8.345864534932186</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6477</v>
+        <v>6214</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>658.0478490004643</v>
+        <v>668.6864300536193</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>38.15</v>
+        <v>180</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>55.72512722557666</v>
+        <v>76.5122677229144</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>18.49536219599972</v>
+        <v>24.581916718812</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.626470104436301</v>
+        <v>0.9686430053619376</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.3145447621248758</v>
+        <v>3.355433643820879</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6419</v>
+        <v>6187</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>657.8893749392804</v>
+        <v>658.3232231159247</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>161</v>
+        <v>1265</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>57.43201544169321</v>
+        <v>57.69850315503145</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>23.1708957729348</v>
+        <v>20.94702745828262</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.6928352351947524</v>
+        <v>0.8620860935134772</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>2.671763104552821</v>
+        <v>24.7018904088973</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -951,21 +951,21 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6279</v>
+        <v>6477</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>645.5192098009226</v>
+        <v>658.0478490004643</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>127.5</v>
+        <v>38.15</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>60.88161936278981</v>
+        <v>55.72512722557666</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>21.01082935032389</v>
+        <v>18.49536219599972</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.3631456072458361</v>
+        <v>1.626470104436301</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.4976983395346135</v>
+        <v>0.3145447621248758</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6224</v>
+        <v>6419</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>626.0720012408416</v>
+        <v>657.8893749392804</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>72.09999999999999</v>
+        <v>161</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>65.34146516200838</v>
+        <v>57.43201544169321</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>24.50487095144129</v>
+        <v>23.1708957729348</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.945015527111977</v>
+        <v>0.6928352351947524</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>2.288242711786421</v>
+        <v>2.671763104552821</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6456</v>
+        <v>6279</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>623.4280069350192</v>
+        <v>645.5192098009226</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>71.2</v>
+        <v>127.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>59.2749281330111</v>
+        <v>60.88161936278981</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>15.53774314714405</v>
+        <v>21.01082935032389</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2.595241213165076</v>
+        <v>0.3631456072458361</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1.076125706553307</v>
+        <v>0.4976983395346135</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6416</v>
+        <v>6224</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>621.6824112927358</v>
+        <v>626.0720012408416</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>102.5</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>58.06976856458292</v>
+        <v>65.34146516200838</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>17.05308785063638</v>
+        <v>24.50487095144129</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.841845922642621</v>
+        <v>2.945015527111977</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.3204899138572403</v>
+        <v>2.288242711786421</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6206</v>
+        <v>6456</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>616.8012753561745</v>
+        <v>623.4280069350192</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>142.5</v>
+        <v>71.2</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>52.71147304673902</v>
+        <v>59.2749281330111</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>28.29508001612185</v>
+        <v>15.53774314714405</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.3258495694000528</v>
+        <v>2.595241213165076</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.09149286289837549</v>
+        <v>1.076125706553307</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6292</v>
+        <v>6416</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>587.1583988586082</v>
+        <v>621.6824112927358</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>61.8</v>
+        <v>102.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>56.2088685271976</v>
+        <v>58.06976856458292</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>25.97496685471785</v>
+        <v>17.05308785063638</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.3648450974704238</v>
+        <v>2.841845922642621</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.4509188348175361</v>
+        <v>-0.3204899138572403</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6278</v>
+        <v>6206</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>575.9939330964177</v>
+        <v>616.8012753561745</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>180</v>
+        <v>142.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>56.56741693871005</v>
+        <v>52.71147304673902</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>17.7528040439102</v>
+        <v>28.29508001612185</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.098034930972146</v>
+        <v>0.3258495694000528</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>3.697311305499584</v>
+        <v>-0.09149286289837549</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6446</v>
+        <v>6292</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>575.0973554913894</v>
+        <v>587.1583988586082</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1375</v>
+        <v>61.8</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>56.07434444851496</v>
+        <v>56.2088685271976</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>31.95886074111771</v>
+        <v>25.97496685471785</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.6471073664331207</v>
+        <v>0.3648450974704238</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>7.599267654557344</v>
+        <v>0.4509188348175361</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6277</v>
+        <v>6278</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>557.6630345415886</v>
+        <v>575.9939330964177</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>81.5</v>
+        <v>180</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>54.370102929117</v>
+        <v>56.56741693871005</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>43.28015408785414</v>
+        <v>17.7528040439102</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.259263695261973</v>
+        <v>1.098034930972146</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.2556532745466207</v>
+        <v>3.697311305499584</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6177</v>
+        <v>6446</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>543.2120434758901</v>
+        <v>575.0973554913894</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>47.05</v>
+        <v>1375</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>45.807496370113</v>
+        <v>56.07434444851496</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>25.50424225120231</v>
+        <v>31.95886074111771</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>3.204867760323918</v>
+        <v>0.6471073664331207</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.0798071852740623</v>
+        <v>7.599267654557344</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6474</v>
+        <v>6277</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>520.2810380964168</v>
+        <v>557.6630345415886</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>39.7</v>
+        <v>81.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>60.82983479329745</v>
+        <v>54.370102929117</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>14.70971460938104</v>
+        <v>43.28015408785414</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.442938511570201</v>
+        <v>1.259263695261973</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.1721479013296802</v>
+        <v>0.2556532745466207</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6449</v>
+        <v>6177</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>520.0373799851818</v>
+        <v>543.2120434758901</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>223</v>
+        <v>47.05</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>40.56801590749667</v>
+        <v>45.807496370113</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>27.42439833240395</v>
+        <v>25.50424225120231</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.4237554791741574</v>
+        <v>3.204867760323918</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>3.330733650849773</v>
+        <v>-0.0798071852740623</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6435</v>
+        <v>6474</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>508.1818815015686</v>
+        <v>520.2810380964168</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>253.5</v>
+        <v>39.7</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>44.12634690426517</v>
+        <v>60.82983479329745</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>21.8439856434628</v>
+        <v>14.70971460938104</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.6782429289345694</v>
+        <v>1.442938511570201</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>2.633334119653941</v>
+        <v>0.1721479013296802</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6464</v>
+        <v>6449</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>504.3193889424014</v>
+        <v>520.0373799851818</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>79</v>
+        <v>223</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>54.87309753426901</v>
+        <v>40.56801590749667</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>28.61802253087765</v>
+        <v>27.42439833240395</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.3864577942800623</v>
+        <v>0.4237554791741574</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.1177869615930627</v>
+        <v>3.330733650849773</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6415</v>
+        <v>6435</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>501.2370325518392</v>
+        <v>508.1818815015686</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>448</v>
+        <v>253.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>46.53499393740031</v>
+        <v>44.12634690426517</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>14.37952197417412</v>
+        <v>21.8439856434628</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.3438889527044256</v>
+        <v>0.6782429289345694</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>4.870674146600217</v>
+        <v>2.633334119653941</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6271</v>
+        <v>6464</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>498.9487396110967</v>
+        <v>504.3193889424014</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>196</v>
+        <v>79</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>48.73962900465847</v>
+        <v>54.87309753426901</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>16.60503326328894</v>
+        <v>28.61802253087765</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.3362079054929519</v>
+        <v>0.3864577942800623</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>3.257129376822347</v>
+        <v>0.1177869615930627</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6183</v>
+        <v>6415</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>486.8821918210058</v>
+        <v>501.2370325518392</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>93.3</v>
+        <v>448</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>55.55228408140169</v>
+        <v>46.53499393740031</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>31.92101045801043</v>
+        <v>14.37952197417412</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.5680335085671625</v>
+        <v>0.3438889527044256</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.012913161081698</v>
+        <v>4.870674146600217</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6291</v>
+        <v>6271</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>482.2524499724996</v>
+        <v>498.9487396110967</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>378.5</v>
+        <v>196</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>46.38601925575917</v>
+        <v>48.73962900465847</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>19.93412347783806</v>
+        <v>16.60503326328894</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5174116584280667</v>
+        <v>0.3362079054929519</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>7.333215360045759</v>
+        <v>3.257129376822347</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1905,21 +1905,21 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6261</v>
+        <v>6183</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>481.0211943090854</v>
+        <v>486.8821918210058</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>77.7</v>
+        <v>93.3</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>41.706018982262</v>
+        <v>55.55228408140169</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>31.85123843382361</v>
+        <v>31.92101045801043</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.5625252438180092</v>
+        <v>0.5680335085671625</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.6495432219893722</v>
+        <v>0.012913161081698</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6274</v>
+        <v>6291</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>481.0017126883812</v>
+        <v>482.2524499724996</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1575</v>
+        <v>378.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>56.0216851925388</v>
+        <v>46.38601925575917</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>12.60665180444862</v>
+        <v>19.93412347783806</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.7882926961721397</v>
+        <v>0.5174116584280667</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>23.68252546407915</v>
+        <v>7.333215360045759</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6405</v>
+        <v>6261</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>480.5959616925842</v>
+        <v>481.0211943090854</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>38.8</v>
+        <v>77.7</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>39.18519180195302</v>
+        <v>41.706018982262</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>27.53533586966542</v>
+        <v>31.85123843382361</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.4497420488416653</v>
+        <v>0.5625252438180092</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.8800216126236684</v>
+        <v>0.6495432219893722</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2064,21 +2064,21 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6207</v>
+        <v>6274</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>468.7569915598773</v>
+        <v>481.0017126883812</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>103</v>
+        <v>1575</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>43.0557357631338</v>
+        <v>56.0216851925388</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>17.61530287792379</v>
+        <v>12.60665180444862</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.3306709481380669</v>
+        <v>0.7882926961721397</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.9831626376038044</v>
+        <v>23.68252546407915</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6470</v>
+        <v>6405</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>467.6706002343219</v>
+        <v>480.5959616925842</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>41.75</v>
+        <v>38.8</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>29.24174825075832</v>
+        <v>39.18519180195302</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45.51663219797959</v>
+        <v>27.53533586966542</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.2979067105022302</v>
+        <v>0.4497420488416653</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,48 +2160,48 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.0198530451491045</v>
+        <v>0.8800216126236684</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6163</v>
+        <v>6207</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>466.408449845447</v>
+        <v>468.7569915598773</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>41.6</v>
+        <v>103</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>46.59206344650912</v>
+        <v>43.0557357631338</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>20.73494114967625</v>
+        <v>17.61530287792379</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.559274377977842</v>
+        <v>0.3306709481380669</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.6177929642924813</v>
+        <v>0.9831626376038044</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6164</v>
+        <v>6470</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>459.9478170687576</v>
+        <v>467.6706002343219</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>11.9</v>
+        <v>41.75</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>45.84705818195098</v>
+        <v>29.24174825075832</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>26.41143847237977</v>
+        <v>45.51663219797959</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.5397335740145272</v>
+        <v>0.2979067105022302</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,48 +2266,48 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.0775003728257429</v>
+        <v>0.0198530451491045</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6191</v>
+        <v>6163</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>華電網</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>459.3332168832501</v>
+        <v>466.408449845447</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>82.59999999999999</v>
+        <v>41.6</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G35" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>38.13748130090197</v>
+        <v>46.59206344650912</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>27.49850669999025</v>
+        <v>20.73494114967625</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.3929505357282586</v>
+        <v>0.559274377977842</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.3848393245099708</v>
+        <v>0.6177929642924813</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2329,21 +2329,21 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6243</v>
+        <v>6164</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>451.751169016772</v>
+        <v>459.9478170687576</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>42.85</v>
+        <v>11.9</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>45.50329035522724</v>
+        <v>45.84705818195098</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>19.56414855458862</v>
+        <v>26.41143847237977</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.2740507645300283</v>
+        <v>0.5397335740145272</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.8795428166878106</v>
+        <v>0.0775003728257429</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6218</v>
+        <v>6191</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>445.0374646604045</v>
+        <v>459.3332168832501</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>38</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>60.56127785203316</v>
+        <v>38.13748130090197</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>20.57491532587705</v>
+        <v>27.49850669999025</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.9351947771513696</v>
+        <v>0.3929505357282586</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.5985980851525227</v>
+        <v>0.3848393245099708</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6190</v>
+        <v>6243</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>444.85960858768</v>
+        <v>451.751169016772</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>65.2</v>
+        <v>42.85</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>40.88085004066118</v>
+        <v>45.50329035522724</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>29.40094615101948</v>
+        <v>19.56414855458862</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.6846789007947829</v>
+        <v>0.2740507645300283</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.332168143529818</v>
+        <v>-0.8795428166878106</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6204</v>
+        <v>6218</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>444.0584752789927</v>
+        <v>445.0374646604045</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>83.3</v>
+        <v>38</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>51.97305234199003</v>
+        <v>60.56127785203316</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>20.12294263343871</v>
+        <v>20.57491532587705</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.358859844036695</v>
+        <v>0.9351947771513696</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>1.904927462033384</v>
+        <v>0.5985980851525227</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6290</v>
+        <v>6190</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>443.7937428630981</v>
+        <v>444.85960858768</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>214.5</v>
+        <v>65.2</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>42.08014479133162</v>
+        <v>40.88085004066118</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>31.6465128318716</v>
+        <v>29.40094615101948</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.351018591620028</v>
+        <v>0.6846789007947829</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>3.46921868139888</v>
+        <v>0.332168143529818</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2594,21 +2594,21 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6409</v>
+        <v>6204</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>443.0864034605569</v>
+        <v>444.0584752789927</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>1040</v>
+        <v>83.3</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>54.69938053965807</v>
+        <v>51.97305234199003</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>17.69608555885018</v>
+        <v>20.12294263343871</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.8523353440979693</v>
+        <v>1.358859844036695</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>6.619009716251898</v>
+        <v>1.904927462033384</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6451</v>
+        <v>6290</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>440.9198289522986</v>
+        <v>443.7937428630981</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>437</v>
+        <v>214.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>49.74707598965418</v>
+        <v>42.08014479133162</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>13.08633955229477</v>
+        <v>31.6465128318716</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.605655744744075</v>
+        <v>1.351018591620028</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>6.316962523979619</v>
+        <v>3.46921868139888</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6417</v>
+        <v>6409</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>438.0080170417768</v>
+        <v>443.0864034605569</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>109</v>
+        <v>1040</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>40.28256268781495</v>
+        <v>54.69938053965807</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>23.56317017632236</v>
+        <v>17.69608555885018</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.453709330733872</v>
+        <v>0.8523353440979693</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.09859868069055271</v>
+        <v>6.619009716251898</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6263</v>
+        <v>6451</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>437.5275788594648</v>
+        <v>440.9198289522986</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>162.5</v>
+        <v>437</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>56.0263115427468</v>
+        <v>49.74707598965418</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>10.52263007106954</v>
+        <v>13.08633955229477</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.6199411402396707</v>
+        <v>1.605655744744075</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>1.174047781946993</v>
+        <v>6.316962523979619</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6230</v>
+        <v>6417</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>426.7603407972766</v>
+        <v>438.0080170417768</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>41.07602077043312</v>
+        <v>40.28256268781495</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>21.40470203392823</v>
+        <v>23.56317017632236</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.5687245258806116</v>
+        <v>0.453709330733872</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,48 +2849,48 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.4032076853008854</v>
+        <v>0.09859868069055271</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6170</v>
+        <v>6263</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>425.4862530857701</v>
+        <v>437.5275788594648</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>47.55</v>
+        <v>162.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G46" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>50.57272402473389</v>
+        <v>56.0263115427468</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>26.41659117018391</v>
+        <v>10.52263007106954</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.8899421073946617</v>
+        <v>0.6199411402396707</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.3072012355637942</v>
+        <v>1.174047781946993</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6227</v>
+        <v>6230</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>424.1469294217599</v>
+        <v>426.7603407972766</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>47.59394129280066</v>
+        <v>41.07602077043312</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>13.49455488884058</v>
+        <v>21.40470203392823</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.5589763059757166</v>
+        <v>0.5687245258806116</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,48 +2955,48 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.5205234061291595</v>
+        <v>0.4032076853008854</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6269</v>
+        <v>6170</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>421.7122519124084</v>
+        <v>425.4862530857701</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>63.6</v>
+        <v>47.55</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G48" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>52.68795057365679</v>
+        <v>50.57272402473389</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>19.20880835862621</v>
+        <v>26.41659117018391</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.3683904838385168</v>
+        <v>0.8899421073946617</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.6372819878051753</v>
+        <v>0.3072012355637942</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6175</v>
+        <v>6227</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>420.1889774242134</v>
+        <v>424.1469294217599</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>74.7</v>
+        <v>118</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>39.59579377928071</v>
+        <v>47.59394129280066</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>19.84951444118018</v>
+        <v>13.49455488884058</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4035384561256389</v>
+        <v>0.5589763059757166</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.8583780267755943</v>
+        <v>-0.5205234061291595</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6174</v>
+        <v>6269</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>419.6405920010851</v>
+        <v>421.7122519124084</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>44.2</v>
+        <v>63.6</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>48.17380396833549</v>
+        <v>52.68795057365679</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>17.9249867828769</v>
+        <v>19.20880835862621</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.5608995263675525</v>
+        <v>0.3683904838385168</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.5799796173542824</v>
+        <v>0.6372819878051753</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3124,21 +3124,21 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6209</v>
+        <v>6175</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>416.2895548542482</v>
+        <v>420.1889774242134</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>69</v>
+        <v>74.7</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>46.0261354326736</v>
+        <v>39.59579377928071</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>13.41039585920414</v>
+        <v>19.84951444118018</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.7426167739036443</v>
+        <v>0.4035384561256389</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0637162553777046</v>
+        <v>0.8583780267755943</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6257</v>
+        <v>6174</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>415.7238747845634</v>
+        <v>419.6405920010851</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>199.5</v>
+        <v>44.2</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>44.12153316133092</v>
+        <v>48.17380396833549</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>14.90528665108752</v>
+        <v>17.9249867828769</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.8674747624194884</v>
+        <v>0.5608995263675525</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.7094721297955395</v>
+        <v>0.5799796173542824</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3230,21 +3230,21 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6245</v>
+        <v>6209</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>414.9941512246751</v>
+        <v>416.2895548542482</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>82.40000000000001</v>
+        <v>69</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>49.62390601414638</v>
+        <v>46.0261354326736</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>13.27554748719096</v>
+        <v>13.41039585920414</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.4659771721048203</v>
+        <v>0.7426167739036443</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.066324298184367</v>
+        <v>0.0637162553777046</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6414</v>
+        <v>6257</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>413.956854684466</v>
+        <v>415.7238747845634</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>402.5</v>
+        <v>199.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>44.23402283668793</v>
+        <v>44.12153316133092</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>18.58562402384953</v>
+        <v>14.90528665108752</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.4956827582394782</v>
+        <v>0.8674747624194884</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,51 +3326,51 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-8.896290194663429</v>
+        <v>0.7094721297955395</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6423</v>
+        <v>6245</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>413.1165578247652</v>
+        <v>414.9941512246751</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>78.90000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G55" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>53.04745037958888</v>
+        <v>49.62390601414638</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>19.71849512887331</v>
+        <v>13.27554748719096</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.5942954256091518</v>
+        <v>0.4659771721048203</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>1.022857926418947</v>
+        <v>-0.066324298184367</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6284</v>
+        <v>6414</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>409.1376754697969</v>
+        <v>413.956854684466</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>77</v>
+        <v>402.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>45.10200174490149</v>
+        <v>44.23402283668793</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>20.90823240888228</v>
+        <v>18.58562402384953</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.6301962788080014</v>
+        <v>0.4956827582394782</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,51 +3432,51 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>1.046127632139643</v>
+        <v>-8.896290194663429</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6226</v>
+        <v>6423</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>光鼎</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>407.7057538243473</v>
+        <v>413.1165578247652</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>22</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G57" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>55.19346732130345</v>
+        <v>53.04745037958888</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>16.60143417011098</v>
+        <v>19.71849512887331</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.082330664499343</v>
+        <v>0.5942954256091518</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.0214891593325286</v>
+        <v>1.022857926418947</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6285</v>
+        <v>6284</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>401.2216222764409</v>
+        <v>409.1376754697969</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>237</v>
+        <v>77</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>46.2303636667012</v>
+        <v>45.10200174490149</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>16.41380157994049</v>
+        <v>20.90823240888228</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.5271609807493075</v>
+        <v>0.6301962788080014</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,51 +3538,51 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.1789910990733414</v>
+        <v>1.046127632139643</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6167</v>
+        <v>6226</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>400.444116371912</v>
+        <v>407.7057538243473</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>10.65</v>
+        <v>22</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G59" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>47.56950574697692</v>
+        <v>55.19346732130345</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>16.68458435225375</v>
+        <v>16.60143417011098</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.6160110163456002</v>
+        <v>1.082330664499343</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0798744540671064</v>
+        <v>-0.0214891593325286</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6197</v>
+        <v>6285</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>399.2454321712863</v>
+        <v>401.2216222764409</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>300.5</v>
+        <v>237</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>46.95623911264508</v>
+        <v>46.2303636667012</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>16.24746368521701</v>
+        <v>16.41380157994049</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.377424212525992</v>
+        <v>0.5271609807493075</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,51 +3644,51 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.6070601194118321</v>
+        <v>-0.1789910990733414</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6239</v>
+        <v>6167</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>398.3707629984119</v>
+        <v>400.444116371912</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>268.5</v>
+        <v>10.65</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G61" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>46.67344648690332</v>
+        <v>47.56950574697692</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>14.46635539806486</v>
+        <v>16.68458435225375</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.3851006925245172</v>
+        <v>0.6160110163456002</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>2.245413529308715</v>
+        <v>0.0798744540671064</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6411</v>
+        <v>6197</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>388.0968146666282</v>
+        <v>399.2454321712863</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>78.90000000000001</v>
+        <v>300.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>45.83381891111971</v>
+        <v>46.95623911264508</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>19.76311929503063</v>
+        <v>16.24746368521701</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.5444013947627107</v>
+        <v>0.377424212525992</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.9342491182998676</v>
+        <v>0.6070601194118321</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6237</v>
+        <v>6239</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>383.4305690117193</v>
+        <v>398.3707629984119</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>34</v>
+        <v>268.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>42.74943345441252</v>
+        <v>46.67344648690332</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>28.46911553908221</v>
+        <v>14.46635539806486</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.3925894057935862</v>
+        <v>0.3851006925245172</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.4082495286505283</v>
+        <v>2.245413529308715</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6259</v>
+        <v>6411</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>380.0811308637175</v>
+        <v>388.0968146666282</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>29.85</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>43.9605967113772</v>
+        <v>45.83381891111971</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>12.48242670259148</v>
+        <v>19.76311929503063</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.6372694363417979</v>
+        <v>0.5444013947627107</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.1218487006745234</v>
+        <v>0.9342491182998676</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6192</v>
+        <v>6237</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>374.5585352154393</v>
+        <v>383.4305690117193</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>117</v>
+        <v>34</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>51.21213486567756</v>
+        <v>42.74943345441252</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>19.96870530628636</v>
+        <v>28.46911553908221</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.441431673274347</v>
+        <v>0.3925894057935862</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.3930436308529887</v>
+        <v>0.4082495286505283</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6168</v>
+        <v>6259</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>374.3130783469072</v>
+        <v>380.0811308637175</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>25</v>
+        <v>29.85</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>50.67504163419478</v>
+        <v>43.9605967113772</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>14.0605526007454</v>
+        <v>12.48242670259148</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.243245715786992</v>
+        <v>0.6372694363417979</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.254158411833506</v>
+        <v>0.1218487006745234</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -3972,21 +3972,21 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6215</v>
+        <v>6192</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>373.0431881224573</v>
+        <v>374.5585352154393</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>99.2</v>
+        <v>117</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>48.03169887542874</v>
+        <v>51.21213486567756</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>18.03381282869475</v>
+        <v>19.96870530628636</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.104115470729832</v>
+        <v>0.441431673274347</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.8526675904485105</v>
+        <v>0.3930436308529887</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6234</v>
+        <v>6168</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>367.4567640608129</v>
+        <v>374.3130783469072</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>35.45</v>
+        <v>25</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>45.45653990295435</v>
+        <v>50.67504163419478</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>22.71452927951729</v>
+        <v>14.0605526007454</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3128675148175951</v>
+        <v>1.243245715786992</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.4930197341313593</v>
+        <v>0.254158411833506</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6233</v>
+        <v>6215</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>365.6529976626165</v>
+        <v>373.0431881224573</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>21.25</v>
+        <v>99.2</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>44.69143054016629</v>
+        <v>48.03169887542874</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>20.13580028982406</v>
+        <v>18.03381282869475</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.2411208744944617</v>
+        <v>1.104115470729832</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,51 +4121,51 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.16816376359578</v>
+        <v>0.8526675904485105</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6288</v>
+        <v>6234</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>聯嘉</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>360.0636317263429</v>
+        <v>367.4567640608129</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>20.95</v>
+        <v>35.45</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G70" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>54.36034424054161</v>
+        <v>45.45653990295435</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>22.53272945130967</v>
+        <v>22.71452927951729</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.6831032524092705</v>
+        <v>0.3128675148175951</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,48 +4174,48 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0242074415559866</v>
+        <v>0.4930197341313593</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6176</v>
+        <v>6233</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>357.6513352023769</v>
+        <v>365.6529976626165</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>81.3</v>
+        <v>21.25</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G71" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>36.44665884902703</v>
+        <v>44.69143054016629</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>23.20465664470696</v>
+        <v>20.13580028982406</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.005858288434822</v>
+        <v>0.2411208744944617</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,51 +4227,51 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.1723411047383507</v>
+        <v>0.16816376359578</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6244</v>
+        <v>6288</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>聯嘉</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>356.5966280460476</v>
+        <v>360.0636317263429</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>24.95</v>
+        <v>20.95</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="G72" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>49.99566094550313</v>
+        <v>54.36034424054161</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>19.30354725283952</v>
+        <v>22.53272945130967</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.367924837577505</v>
+        <v>0.6831032524092705</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,48 +4280,48 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.329541600507905</v>
+        <v>0.0242074415559866</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6216</v>
+        <v>6176</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>353.9479800727557</v>
+        <v>357.6513352023769</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>22.3</v>
+        <v>81.3</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G73" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>51.36708791101365</v>
+        <v>36.44665884902703</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>11.35658320057852</v>
+        <v>23.20465664470696</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.6006513730445461</v>
+        <v>1.005858288434822</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.0541247093542724</v>
+        <v>-0.1723411047383507</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6196</v>
+        <v>6244</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>349.5582056117107</v>
+        <v>356.5966280460476</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>496</v>
+        <v>24.95</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>45.82052899686781</v>
+        <v>49.99566094550313</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>11.48743139707862</v>
+        <v>19.30354725283952</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.5194043713330911</v>
+        <v>0.367924837577505</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>1.366281794286349</v>
+        <v>0.329541600507905</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6202</v>
+        <v>6216</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>343.855664284434</v>
+        <v>353.9479800727557</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>57.3</v>
+        <v>22.3</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>45.84151871726803</v>
+        <v>51.36708791101365</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>15.34445898948009</v>
+        <v>11.35658320057852</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.3999766488670502</v>
+        <v>0.6006513730445461</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0264056687515031</v>
+        <v>0.0541247093542724</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6282</v>
+        <v>6196</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>339.7469040021632</v>
+        <v>349.5582056117107</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>45</v>
+        <v>496</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>41.15947052804628</v>
+        <v>45.82052899686781</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>17.38712751702644</v>
+        <v>11.48743139707862</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.6217586562517554</v>
+        <v>0.5194043713330911</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.2226193056363348</v>
+        <v>1.366281794286349</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4502,21 +4502,21 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6182</v>
+        <v>6202</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>337.3975744880566</v>
+        <v>343.855664284434</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>109.5</v>
+        <v>57.3</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>48.18740732380431</v>
+        <v>45.84151871726803</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>17.7447435643948</v>
+        <v>15.34445898948009</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.287327346385756</v>
+        <v>0.3999766488670502</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>2.0103619596286</v>
+        <v>0.0264056687515031</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4555,41 +4555,41 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6241</v>
+        <v>6282</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>鑫永洋</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>325.5169087677943</v>
+        <v>339.7469040021632</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>13.85</v>
+        <v>45</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G78" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>37.93433998246152</v>
+        <v>41.15947052804628</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>23.71245664322524</v>
+        <v>17.38712751702644</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.9224191436906496</v>
+        <v>0.6217586562517554</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.3588733291969993</v>
+        <v>0.2226193056363348</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6441</v>
+        <v>6182</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>324.5267979812926</v>
+        <v>337.3975744880566</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>21.7</v>
+        <v>109.5</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>50.2921773008302</v>
+        <v>48.18740732380431</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>21.90746939727575</v>
+        <v>17.7447435643948</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.4119354585632469</v>
+        <v>1.287327346385756</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,51 +4651,51 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.1055049941016015</v>
+        <v>2.0103619596286</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6442</v>
+        <v>6241</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>鑫永洋</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>324.1119776828579</v>
+        <v>325.5169087677943</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>1555</v>
+        <v>13.85</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G80" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>55.05675363330204</v>
+        <v>37.93433998246152</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>19.95906951800938</v>
+        <v>23.71245664322524</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.7551822328604415</v>
+        <v>0.9224191436906496</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>35.42092947675899</v>
+        <v>-0.3588733291969993</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6443</v>
+        <v>6441</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>320.1166023860689</v>
+        <v>324.5267979812926</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>26.1</v>
+        <v>21.7</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>42.04170327674651</v>
+        <v>50.2921773008302</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>18.3883686311362</v>
+        <v>21.90746939727575</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.448574025134252</v>
+        <v>0.4119354585632469</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.3607007690135062</v>
+        <v>0.1055049941016015</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6229</v>
+        <v>6442</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>307.5273826016369</v>
+        <v>324.1119776828579</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>23.55</v>
+        <v>1555</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>44.53471012224625</v>
+        <v>55.05675363330204</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>16.77277246299333</v>
+        <v>19.95906951800938</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.5725990038283573</v>
+        <v>0.7551822328604415</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.179650122016915</v>
+        <v>35.42092947675899</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6412</v>
+        <v>6443</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>305.1459806011048</v>
+        <v>320.1166023860689</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>26.1</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>43.24095658461552</v>
+        <v>42.04170327674651</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>28.43432288811318</v>
+        <v>18.3883686311362</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.5790609368786639</v>
+        <v>0.448574025134252</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.3359390890513554</v>
+        <v>0.3607007690135062</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6246</v>
+        <v>6229</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>302.0901855747236</v>
+        <v>307.5273826016369</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>12.35</v>
+        <v>23.55</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>41.19134367516796</v>
+        <v>44.53471012224625</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>20.70433834805672</v>
+        <v>16.77277246299333</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.1503835762988442</v>
+        <v>0.5725990038283573</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.08148894123035159</v>
+        <v>0.179650122016915</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6465</v>
+        <v>6412</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>301.7040768987792</v>
+        <v>305.1459806011048</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>45.75</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>33.5655620738771</v>
+        <v>43.24095658461552</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>14.31020074735301</v>
+        <v>28.43432288811318</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.4151348907786417</v>
+        <v>0.5790609368786639</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.2498175913689482</v>
+        <v>0.3359390890513554</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6418</v>
+        <v>6246</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>298.4573210421664</v>
+        <v>302.0901855747236</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>33</v>
+        <v>12.35</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>56.40106537892555</v>
+        <v>41.19134367516796</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>18.32875407024433</v>
+        <v>20.70433834805672</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.5483920466076316</v>
+        <v>0.1503835762988442</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.1451460878453163</v>
+        <v>0.08148894123035159</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6266</v>
+        <v>6465</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>297.3050655370212</v>
+        <v>301.7040768987792</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>25.1</v>
+        <v>45.75</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>52.33917502773247</v>
+        <v>33.5655620738771</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>13.71204564473456</v>
+        <v>14.31020074735301</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.4506801546407011</v>
+        <v>0.4151348907786417</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.1165640214307519</v>
+        <v>0.2498175913689482</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6432</v>
+        <v>6418</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>287.8946864817354</v>
+        <v>298.4573210421664</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>66.5</v>
+        <v>33</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>42.1541070570314</v>
+        <v>56.40106537892555</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>10.8415108157783</v>
+        <v>18.32875407024433</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.2782383949391305</v>
+        <v>0.5483920466076316</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.728783914412474</v>
+        <v>0.1451460878453163</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6270</v>
+        <v>6266</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>283.0679885136168</v>
+        <v>297.3050655370212</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>30.15</v>
+        <v>25.1</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>46.86274322647808</v>
+        <v>52.33917502773247</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>11.41783764329637</v>
+        <v>13.71204564473456</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.5243484751740956</v>
+        <v>0.4506801546407011</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.2679781971712429</v>
+        <v>0.1165640214307519</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6165</v>
+        <v>6432</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>281.801291578759</v>
+        <v>287.8946864817354</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>47.35</v>
+        <v>66.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>41.68556858783962</v>
+        <v>42.1541070570314</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>12.83281861799132</v>
+        <v>10.8415108157783</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.1757203910445993</v>
+        <v>0.2782383949391305</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.2969322807929263</v>
+        <v>-0.728783914412474</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6281</v>
+        <v>6270</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>280.4049443031774</v>
+        <v>283.0679885136168</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>51.5</v>
+        <v>30.15</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>49.64480629767314</v>
+        <v>46.86274322647808</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>15.21679398210964</v>
+        <v>11.41783764329637</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5064696629541791</v>
+        <v>0.5243484751740956</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.0433697078571478</v>
+        <v>0.2679781971712429</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, williams_r_recovery</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6438</v>
+        <v>6165</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>277.3157741892858</v>
+        <v>281.801291578759</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>143.5</v>
+        <v>47.35</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>47.4071973337609</v>
+        <v>41.68556858783962</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>16.5938735413248</v>
+        <v>12.83281861799132</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.7429019508908455</v>
+        <v>0.1757203910445993</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.483037782164565</v>
+        <v>-0.2969322807929263</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6462</v>
+        <v>6281</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>275.1390649471618</v>
+        <v>280.4049443031774</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>98.5</v>
+        <v>51.5</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>44.81907596233921</v>
+        <v>49.64480629767314</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>15.65457343806104</v>
+        <v>15.21679398210964</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.5905198992111346</v>
+        <v>0.5064696629541791</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.6323976747462736</v>
+        <v>-0.0433697078571478</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6189</v>
+        <v>6438</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>274.0920656968739</v>
+        <v>277.3157741892858</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>48.15</v>
+        <v>143.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>47.06893588306007</v>
+        <v>47.4071973337609</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>10.46035017901697</v>
+        <v>16.5938735413248</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.6507692071564148</v>
+        <v>0.7429019508908455</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0448057298431924</v>
+        <v>0.483037782164565</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5456,21 +5456,21 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6205</v>
+        <v>6462</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>273.0433406709475</v>
+        <v>275.1390649471618</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>61.4</v>
+        <v>98.5</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>46.32480753365101</v>
+        <v>44.81907596233921</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>18.46072316242684</v>
+        <v>15.65457343806104</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.3534355855128882</v>
+        <v>0.5905198992111346</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.820252458475879</v>
+        <v>0.6323976747462736</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6236</v>
+        <v>6189</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>272.2577858006088</v>
+        <v>274.0920656968739</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>0</v>
+        <v>48.15</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>47.45493102430352</v>
+        <v>47.06893588306007</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>9.673925890943224</v>
+        <v>10.46035017901697</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0</v>
+        <v>0.6507692071564148</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0289905944715258</v>
+        <v>0.0448057298431924</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6217</v>
+        <v>6205</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>271.5683227325385</v>
+        <v>273.0433406709475</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>153.5</v>
+        <v>61.4</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>43.13572405992045</v>
+        <v>46.32480753365101</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>16.71569639668634</v>
+        <v>18.46072316242684</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.290161702150938</v>
+        <v>0.3534355855128882</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>4.805519770690275</v>
+        <v>0.820252458475879</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6166</v>
+        <v>6236</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>中湛</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>269.2005419402724</v>
+        <v>272.2577858006088</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>120.5</v>
+        <v>0</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>41.35778656110351</v>
+        <v>47.45493102430352</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>14.03783188830391</v>
+        <v>9.673925890943224</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.4660016770667697</v>
+        <v>0</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-1.890363801632936</v>
+        <v>-0.0289905944715258</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6272</v>
+        <v>6217</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>263.2236311156739</v>
+        <v>271.5683227325385</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>23.4</v>
+        <v>153.5</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>35.61823411530359</v>
+        <v>43.13572405992045</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>44.11189011180613</v>
+        <v>16.71569639668634</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.3694573178107275</v>
+        <v>1.290161702150938</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.1191815907461535</v>
+        <v>4.805519770690275</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6188</v>
+        <v>6166</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>260.5925801527255</v>
+        <v>269.2005419402724</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>68.7</v>
+        <v>120.5</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>40.61929415513303</v>
+        <v>41.35778656110351</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>19.18220929917588</v>
+        <v>14.03783188830391</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.4757638516146825</v>
+        <v>0.4660016770667697</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.1861939049427605</v>
+        <v>-1.890363801632936</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6283</v>
+        <v>6272</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>259.0146849036807</v>
+        <v>263.2236311156739</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>20</v>
+        <v>23.4</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>37.18239284886904</v>
+        <v>35.61823411530359</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>38.65764919335546</v>
+        <v>44.11189011180613</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.6346616959335815</v>
+        <v>0.3694573178107275</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.09756961557332861</v>
+        <v>0.1191815907461535</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5827,21 +5827,21 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6275</v>
+        <v>6188</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>257.3087142516948</v>
+        <v>260.5925801527255</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>44.2</v>
+        <v>68.7</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>48.62620223830222</v>
+        <v>40.61929415513303</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>18.51726590947178</v>
+        <v>19.18220929917588</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.9371863027301426</v>
+        <v>0.4757638516146825</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.3272718884720997</v>
+        <v>0.1861939049427605</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6194</v>
+        <v>6283</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>251.2893649072785</v>
+        <v>259.0146849036807</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>29.45</v>
+        <v>20</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>35.79526656272576</v>
+        <v>37.18239284886904</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>26.79652759104424</v>
+        <v>38.65764919335546</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.0661905222970854</v>
+        <v>0.6346616959335815</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.068403957509313</v>
+        <v>0.09756961557332861</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6223</v>
+        <v>6275</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>250.8650196720448</v>
+        <v>257.3087142516948</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>5650</v>
+        <v>44.2</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>45.97493746731448</v>
+        <v>48.62620223830222</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>15.12025758078078</v>
+        <v>18.51726590947178</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.140383999820566</v>
+        <v>0.9371863027301426</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-53.11930690724548</v>
+        <v>0.3272718884720997</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6220</v>
+        <v>6194</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>241.8441256046481</v>
+        <v>251.2893649072785</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>25.55</v>
+        <v>29.45</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>37.4146193241935</v>
+        <v>35.79526656272576</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>28.07137385027435</v>
+        <v>26.79652759104424</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.3505144320073916</v>
+        <v>0.0661905222970854</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.2608375492995152</v>
+        <v>0.068403957509313</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6201</v>
+        <v>6223</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>240.0769271138365</v>
+        <v>250.8650196720448</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>44.95</v>
+        <v>5650</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>33.53147234452052</v>
+        <v>45.97493746731448</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>22.92091686473323</v>
+        <v>15.12025758078078</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.2691859480448688</v>
+        <v>1.140383999820566</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.1816436088834629</v>
+        <v>-53.11930690724548</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6185</v>
+        <v>6220</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>221.8343395477669</v>
+        <v>241.8441256046481</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>13.2</v>
+        <v>25.55</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>32.93075387984044</v>
+        <v>37.4146193241935</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>16.05979983508301</v>
+        <v>28.07137385027435</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.605269027030974</v>
+        <v>0.3505144320073916</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0510883275214058</v>
+        <v>0.2608375492995152</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6184</v>
+        <v>6201</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>212.5326700917151</v>
+        <v>240.0769271138365</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>41.65</v>
+        <v>44.95</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>27.42320786994281</v>
+        <v>33.53147234452052</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>16.86036652986773</v>
+        <v>22.92091686473323</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.526437904506045</v>
+        <v>0.2691859480448688</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0250315099350862</v>
+        <v>-0.1816436088834629</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6210</v>
+        <v>6185</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>206.9221473964113</v>
+        <v>221.8343395477669</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>17.4</v>
+        <v>13.2</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>49.71585187009426</v>
+        <v>32.93075387984044</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>9.776981673980332</v>
+        <v>16.05979983508301</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.1093317370899718</v>
+        <v>1.605269027030974</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0917269177955472</v>
+        <v>-0.0510883275214058</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6235</v>
+        <v>6184</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>202.4101597859209</v>
+        <v>212.5326700917151</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>37.85</v>
+        <v>41.65</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>43.60383968303603</v>
+        <v>27.42320786994281</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>13.16900415035904</v>
+        <v>16.86036652986773</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.4357722239158529</v>
+        <v>1.526437904506045</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0211867519270172</v>
+        <v>0.0250315099350862</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6222</v>
+        <v>6210</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>200.8211586477661</v>
+        <v>206.9221473964113</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>20.15</v>
+        <v>17.4</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>51.50815291393139</v>
+        <v>49.71585187009426</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>12.55616701492719</v>
+        <v>9.776981673980332</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.062083614946413</v>
+        <v>0.1093317370899718</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.5071547912441488</v>
+        <v>0.0917269177955472</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6198</v>
+        <v>6235</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>177.961505916352</v>
+        <v>202.4101597859209</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>19.4</v>
+        <v>37.85</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>51.47929556907678</v>
+        <v>43.60383968303603</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>6.677654065306673</v>
+        <v>13.16900415035904</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.55544205070427</v>
+        <v>0.4357722239158529</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.6389302258277995</v>
+        <v>0.0211867519270172</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6208</v>
+        <v>6222</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>167.9630234755384</v>
+        <v>200.8211586477661</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>82.40000000000001</v>
+        <v>20.15</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>46.87970997090247</v>
+        <v>51.50815291393139</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>11.06187678640525</v>
+        <v>12.55616701492719</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.6542251624872468</v>
+        <v>1.062083614946413</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.3950505389604686</v>
+        <v>-0.5071547912441488</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6276</v>
+        <v>6198</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>163.8421247651532</v>
+        <v>177.961505916352</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>42.94397763902317</v>
+        <v>51.47929556907678</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>27.28754019103363</v>
+        <v>6.677654065306673</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.6704197265960952</v>
+        <v>0.55544205070427</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0857566502081212</v>
+        <v>0.6389302258277995</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6228</v>
+        <v>6208</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>159.3697743087402</v>
+        <v>167.9630234755384</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>17.85</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>51.7099752705824</v>
+        <v>46.87970997090247</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>8.988457717556663</v>
+        <v>11.06187678640525</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.2313904250642108</v>
+        <v>0.6542251624872468</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,62 +6559,168 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.4703637373382745</v>
+        <v>0.3950505389604686</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
+        <v>6276</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>安鈦克</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>163.8421247651532</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>42.94397763902317</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>27.28754019103363</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.6704197265960952</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>0.0857566502081212</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>6228</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>全譜</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>159.3697743087402</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>51.7099752705824</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>8.988457717556663</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.2313904250642108</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>0.4703637373382745</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
         <v>6203</v>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>海韻電</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D116" s="2" t="n">
+      <c r="C118" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="n">
         <v>137.5777813443169</v>
       </c>
-      <c r="E116" s="2" t="n">
+      <c r="E118" s="2" t="n">
         <v>60.3</v>
       </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H116" s="2" t="n">
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
         <v>34.04465399237806</v>
       </c>
-      <c r="I116" s="2" t="n">
+      <c r="I118" s="2" t="n">
         <v>17.61271677648816</v>
       </c>
-      <c r="J116" s="2" t="n">
+      <c r="J118" s="2" t="n">
         <v>0.4611482280173328</v>
       </c>
-      <c r="K116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N116" s="2" t="n">
+      <c r="K118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2" t="n">
         <v>-0.009123095530227899</v>
       </c>
-      <c r="O116" s="2" t="inlineStr">
+      <c r="O118" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
